--- a/data/trans_dic/P57GLOBAL_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P57GLOBAL_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (tasa de respuesta: 98,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,8; 85,89</t>
+          <t>76,92; 85,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,33; 83,74</t>
+          <t>73,43; 84,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,01; 88,73</t>
+          <t>79,72; 88,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45,99; 60,59</t>
+          <t>46,07; 60,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,02; 94,11</t>
+          <t>87,09; 94,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,38; 89,81</t>
+          <t>81,51; 90,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,63; 89,8</t>
+          <t>81,03; 89,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55,23; 64,92</t>
+          <t>55,42; 64,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>82,93; 88,91</t>
+          <t>83,03; 88,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78,83; 85,57</t>
+          <t>79,1; 85,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81,7; 88,25</t>
+          <t>82,32; 88,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,46; 61,11</t>
+          <t>52,38; 61,17</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,3; 67,1</t>
+          <t>58,02; 67,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,0; 60,68</t>
+          <t>51,76; 61,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,98; 86,45</t>
+          <t>79,38; 86,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58,26; 68,99</t>
+          <t>57,2; 68,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,06; 73,28</t>
+          <t>65,19; 72,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,17; 63,09</t>
+          <t>54,11; 62,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,33; 85,92</t>
+          <t>79,13; 85,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,67; 61,35</t>
+          <t>53,56; 61,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63,17; 69,21</t>
+          <t>62,8; 68,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54,16; 60,69</t>
+          <t>54,12; 60,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80,72; 85,47</t>
+          <t>80,73; 85,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,93; 63,84</t>
+          <t>57,06; 63,98</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58,7; 69,35</t>
+          <t>58,66; 69,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,5; 71,22</t>
+          <t>61,18; 71,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73,82; 83,19</t>
+          <t>74,04; 83,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42,88; 54,22</t>
+          <t>42,51; 54,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53,65; 64,09</t>
+          <t>52,71; 63,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71,28; 80,73</t>
+          <t>71,62; 80,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,12; 86,94</t>
+          <t>78,81; 86,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,62; 60,06</t>
+          <t>49,8; 59,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,17; 65,07</t>
+          <t>57,45; 64,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67,79; 74,78</t>
+          <t>67,55; 75,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77,73; 83,78</t>
+          <t>77,7; 83,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>47,83; 55,37</t>
+          <t>48,41; 55,76</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>67,49; 77,11</t>
+          <t>67,97; 77,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,51; 58,96</t>
+          <t>48,91; 59,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42,65; 53,29</t>
+          <t>41,98; 52,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,42; 41,08</t>
+          <t>27,46; 41,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,82; 75,67</t>
+          <t>66,57; 75,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,12; 68,22</t>
+          <t>58,08; 68,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,55; 63,44</t>
+          <t>53,36; 63,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,45; 37,68</t>
+          <t>17,89; 36,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>68,72; 75,12</t>
+          <t>68,73; 74,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55,09; 62,38</t>
+          <t>54,96; 62,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49,28; 56,84</t>
+          <t>49,17; 56,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,09; 36,4</t>
+          <t>22,32; 36,28</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,66; 86,46</t>
+          <t>75,11; 86,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51,37; 65,07</t>
+          <t>50,99; 65,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,58; 94,57</t>
+          <t>86,65; 94,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88,24; 95,78</t>
+          <t>87,8; 95,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81,26; 90,85</t>
+          <t>81,79; 91,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,99; 79,94</t>
+          <t>68,02; 80,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,4; 94,67</t>
+          <t>87,47; 94,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>88,91; 94,76</t>
+          <t>89,08; 94,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>79,94; 87,19</t>
+          <t>79,75; 86,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61,32; 70,98</t>
+          <t>61,47; 70,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88,44; 93,92</t>
+          <t>88,56; 93,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>89,55; 94,56</t>
+          <t>89,59; 94,47</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65,95; 76,84</t>
+          <t>66,1; 77,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59,78; 71,64</t>
+          <t>59,75; 71,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74,44; 84,42</t>
+          <t>74,35; 84,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35,49; 46,03</t>
+          <t>35,48; 45,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68,22; 78,65</t>
+          <t>68,53; 78,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,0; 83,2</t>
+          <t>72,82; 82,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76,18; 85,81</t>
+          <t>76,91; 85,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36,5; 45,7</t>
+          <t>36,2; 46,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>68,85; 76,49</t>
+          <t>68,88; 76,59</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>67,34; 75,76</t>
+          <t>67,42; 75,36</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76,99; 83,6</t>
+          <t>76,71; 83,73</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37,0; 44,36</t>
+          <t>37,27; 44,94</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>49,81; 57,85</t>
+          <t>49,82; 58,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>57,91; 65,96</t>
+          <t>57,75; 65,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81,93; 87,64</t>
+          <t>81,61; 87,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60,93; 70,16</t>
+          <t>60,81; 69,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,76; 53,57</t>
+          <t>45,91; 53,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,05; 74,93</t>
+          <t>68,19; 75,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,91; 90,91</t>
+          <t>85,94; 90,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>62,11; 69,67</t>
+          <t>62,12; 69,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>49,11; 54,66</t>
+          <t>49,05; 54,81</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64,25; 69,43</t>
+          <t>64,15; 69,4</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84,9; 88,69</t>
+          <t>84,94; 88,66</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,58; 68,27</t>
+          <t>62,63; 68,77</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>80,41; 85,96</t>
+          <t>80,66; 85,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>89,15; 93,26</t>
+          <t>89,19; 93,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91,17; 94,75</t>
+          <t>91,02; 94,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27,63; 86,31</t>
+          <t>29,5; 86,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>85,78; 90,43</t>
+          <t>85,77; 90,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>87,35; 92,05</t>
+          <t>87,65; 91,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>93,22; 96,43</t>
+          <t>93,27; 96,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>85,83; 90,16</t>
+          <t>85,75; 90,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>84,0; 87,58</t>
+          <t>84,03; 87,54</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88,99; 92,09</t>
+          <t>89,08; 92,06</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>92,72; 95,13</t>
+          <t>92,71; 95,25</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>46,22; 87,52</t>
+          <t>41,66; 87,55</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>68,81; 71,98</t>
+          <t>68,8; 72,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>67,33; 70,42</t>
+          <t>67,28; 70,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>80,69; 83,38</t>
+          <t>80,46; 83,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>44,53; 63,76</t>
+          <t>43,82; 63,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>70,65; 73,61</t>
+          <t>70,66; 73,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>73,71; 76,73</t>
+          <t>73,78; 76,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>83,36; 85,93</t>
+          <t>83,5; 86,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>58,44; 64,94</t>
+          <t>57,68; 64,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>70,14; 72,39</t>
+          <t>70,2; 72,44</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70,94; 73,25</t>
+          <t>71,07; 73,29</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>82,45; 84,33</t>
+          <t>82,49; 84,22</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>51,76; 63,52</t>
+          <t>51,86; 63,55</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (tasa de respuesta: 98,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>209028; 233782</t>
+          <t>209358; 233604</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>207274; 236692</t>
+          <t>207546; 238115</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>228722; 253669</t>
+          <t>227904; 253978</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>141127; 185913</t>
+          <t>141351; 185052</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>226989; 245479</t>
+          <t>227165; 246020</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>225730; 249101</t>
+          <t>226080; 249764</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>229702; 252676</t>
+          <t>227992; 251897</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>158185; 185918</t>
+          <t>158717; 185408</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>442038; 473911</t>
+          <t>442542; 472674</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>441452; 479233</t>
+          <t>442982; 479994</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>463442; 500628</t>
+          <t>466978; 499964</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>311196; 362498</t>
+          <t>310731; 362863</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>285803; 328972</t>
+          <t>284419; 330575</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>261306; 304969</t>
+          <t>260127; 307704</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>397785; 429954</t>
+          <t>394815; 430007</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>299439; 354567</t>
+          <t>293952; 353340</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>327879; 369296</t>
+          <t>328519; 367550</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>283057; 329699</t>
+          <t>282742; 329122</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>410637; 444764</t>
+          <t>409639; 444419</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>274767; 314083</t>
+          <t>274203; 315155</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>627999; 688124</t>
+          <t>624335; 683494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>555173; 622155</t>
+          <t>554805; 622183</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>819380; 867549</t>
+          <t>819461; 865268</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>584012; 654858</t>
+          <t>585301; 656389</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>187162; 221135</t>
+          <t>187046; 221856</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>195422; 230041</t>
+          <t>197610; 230130</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>233758; 263427</t>
+          <t>234440; 262906</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>127249; 160909</t>
+          <t>126174; 161607</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>179933; 214973</t>
+          <t>176803; 213979</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>240828; 272740</t>
+          <t>241986; 271944</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>263361; 289387</t>
+          <t>262340; 287505</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>159937; 189775</t>
+          <t>157350; 187985</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>374040; 425747</t>
+          <t>375903; 424566</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>448023; 494174</t>
+          <t>446403; 496258</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>504863; 544158</t>
+          <t>504699; 542049</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>293092; 339256</t>
+          <t>296624; 341637</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>242074; 276574</t>
+          <t>243776; 276242</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>179840; 218555</t>
+          <t>181304; 220903</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>156910; 196092</t>
+          <t>154453; 193491</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84560; 126702</t>
+          <t>84697; 127314</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>248212; 281063</t>
+          <t>247288; 281009</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>224915; 263978</t>
+          <t>224750; 264255</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>205800; 243810</t>
+          <t>205047; 243331</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>80998; 174892</t>
+          <t>83048; 170882</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>501778; 548507</t>
+          <t>501780; 547428</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>417404; 472613</t>
+          <t>416405; 472928</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>370685; 427552</t>
+          <t>369859; 428363</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>170694; 281237</t>
+          <t>172473; 280307</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>151784; 175788</t>
+          <t>152696; 175809</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>108708; 137694</t>
+          <t>107888; 137534</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>181943; 198753</t>
+          <t>182090; 198748</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>157116; 170548</t>
+          <t>156333; 170676</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>167948; 187765</t>
+          <t>169044; 188305</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>148699; 174835</t>
+          <t>148750; 175455</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>191044; 206933</t>
+          <t>191187; 207149</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>185170; 197359</t>
+          <t>185531; 197280</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>327738; 357473</t>
+          <t>326947; 356598</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>263853; 305429</t>
+          <t>264511; 304195</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>379190; 402681</t>
+          <t>379695; 402712</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>345952; 365330</t>
+          <t>346099; 364972</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>178598; 208089</t>
+          <t>178994; 209533</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>160690; 192553</t>
+          <t>160608; 191286</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>195858; 222118</t>
+          <t>195628; 221494</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>95336; 123649</t>
+          <t>95320; 123231</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>189759; 218754</t>
+          <t>190600; 219080</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>202150; 230376</t>
+          <t>201646; 229294</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>206575; 232688</t>
+          <t>208558; 233139</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>93680; 117301</t>
+          <t>92908; 118117</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>377939; 419919</t>
+          <t>378112; 420428</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>367456; 413419</t>
+          <t>367927; 411246</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>411355; 446686</t>
+          <t>409885; 447377</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>194379; 233030</t>
+          <t>195768; 236088</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>306316; 355799</t>
+          <t>306393; 357057</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>378706; 431298</t>
+          <t>377647; 428193</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>534128; 571350</t>
+          <t>532025; 572591</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>373636; 430238</t>
+          <t>372863; 427035</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>291631; 341372</t>
+          <t>292548; 343080</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>464062; 510997</t>
+          <t>465030; 512682</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>584202; 618188</t>
+          <t>584402; 617481</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>391989; 439682</t>
+          <t>392033; 439966</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>615023; 684514</t>
+          <t>614174; 686318</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>858305; 927532</t>
+          <t>857001; 927140</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1130760; 1181339</t>
+          <t>1131314; 1180842</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>778662; 849471</t>
+          <t>779252; 855675</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>596175; 637338</t>
+          <t>598006; 637039</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>689226; 721036</t>
+          <t>689543; 720784</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>706481; 734219</t>
+          <t>705370; 735402</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>255598; 798506</t>
+          <t>272940; 800012</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>671110; 707476</t>
+          <t>671063; 708091</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>716792; 755391</t>
+          <t>719267; 754712</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>767023; 793399</t>
+          <t>767442; 792952</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>614076; 645079</t>
+          <t>613484; 645193</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1280028; 1334522</t>
+          <t>1280455; 1333922</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1418180; 1467711</t>
+          <t>1419641; 1467239</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1481428; 1519856</t>
+          <t>1481328; 1521897</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>758285; 1435830</t>
+          <t>683443; 1436271</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2250542; 2354164</t>
+          <t>2250039; 2355032</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2280017; 2384626</t>
+          <t>2278392; 2391339</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2717762; 2808146</t>
+          <t>2709949; 2805215</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1518941; 2174881</t>
+          <t>1494593; 2170174</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2385333; 2485211</t>
+          <t>2385562; 2491086</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2596683; 2703225</t>
+          <t>2599356; 2702639</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2924839; 3015188</t>
+          <t>2929722; 3018733</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1980925; 2201273</t>
+          <t>1955444; 2194019</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4661791; 4811229</t>
+          <t>4665905; 4815066</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4901721; 5060829</t>
+          <t>4910688; 5064090</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5669921; 5799050</t>
+          <t>5672689; 5791798</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3520377; 4320061</t>
+          <t>3527222; 4322024</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57GLOBAL_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P57GLOBAL_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>58,52%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,92; 85,83</t>
+          <t>76,32; 85,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,43; 84,24</t>
+          <t>73,87; 84,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,72; 88,84</t>
+          <t>79,52; 88,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46,07; 60,31</t>
+          <t>49,92; 62,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,09; 94,32</t>
+          <t>86,92; 94,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,51; 90,05</t>
+          <t>81,07; 89,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,03; 89,52</t>
+          <t>80,67; 89,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55,42; 64,74</t>
+          <t>56,34; 65,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>83,03; 88,68</t>
+          <t>83,22; 88,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79,1; 85,71</t>
+          <t>78,97; 85,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82,32; 88,14</t>
+          <t>82,11; 88,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,38; 61,17</t>
+          <t>54,68; 62,36</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,79%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,02; 67,43</t>
+          <t>58,61; 67,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,76; 61,23</t>
+          <t>51,85; 61,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,38; 86,46</t>
+          <t>79,81; 86,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57,2; 68,75</t>
+          <t>57,98; 68,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,19; 72,93</t>
+          <t>65,58; 73,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,11; 62,98</t>
+          <t>53,93; 63,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,13; 85,85</t>
+          <t>79,68; 86,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,56; 61,56</t>
+          <t>54,18; 61,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62,8; 68,75</t>
+          <t>63,12; 69,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54,12; 60,69</t>
+          <t>54,53; 60,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80,73; 85,25</t>
+          <t>80,67; 85,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>57,06; 63,98</t>
+          <t>57,18; 64,01</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,71%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58,66; 69,58</t>
+          <t>58,56; 69,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,18; 71,24</t>
+          <t>60,87; 71,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,04; 83,03</t>
+          <t>73,96; 82,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42,51; 54,45</t>
+          <t>43,38; 54,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,71; 63,8</t>
+          <t>52,73; 63,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71,62; 80,49</t>
+          <t>71,57; 81,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,81; 86,37</t>
+          <t>78,77; 86,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49,8; 59,5</t>
+          <t>51,48; 60,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,45; 64,89</t>
+          <t>57,71; 64,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67,55; 75,09</t>
+          <t>68,06; 74,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77,7; 83,45</t>
+          <t>77,51; 83,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,41; 55,76</t>
+          <t>49,2; 56,55</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>67,97; 77,02</t>
+          <t>67,97; 77,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,91; 59,59</t>
+          <t>48,76; 59,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,98; 52,59</t>
+          <t>42,59; 53,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,46; 41,28</t>
+          <t>28,6; 41,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,57; 75,65</t>
+          <t>66,16; 75,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,08; 68,29</t>
+          <t>58,64; 68,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,36; 63,32</t>
+          <t>53,23; 63,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,89; 36,81</t>
+          <t>33,21; 42,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>68,73; 74,98</t>
+          <t>68,49; 74,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54,96; 62,42</t>
+          <t>55,08; 62,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49,17; 56,95</t>
+          <t>49,59; 57,05</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,32; 36,28</t>
+          <t>32,31; 40,24</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>75,11; 86,47</t>
+          <t>75,3; 86,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,99; 65,0</t>
+          <t>51,08; 64,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,65; 94,57</t>
+          <t>86,42; 94,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87,8; 95,85</t>
+          <t>87,57; 95,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81,79; 91,11</t>
+          <t>81,34; 90,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,02; 80,23</t>
+          <t>67,28; 79,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,47; 94,77</t>
+          <t>87,26; 95,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>89,08; 94,72</t>
+          <t>89,32; 95,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>79,75; 86,98</t>
+          <t>80,0; 87,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61,47; 70,69</t>
+          <t>61,34; 70,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88,56; 93,93</t>
+          <t>88,44; 93,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>89,59; 94,47</t>
+          <t>90,05; 94,8</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>42,43%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>66,1; 77,37</t>
+          <t>65,73; 77,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59,75; 71,17</t>
+          <t>58,65; 70,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74,35; 84,18</t>
+          <t>74,46; 84,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35,48; 45,87</t>
+          <t>37,7; 48,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68,53; 78,76</t>
+          <t>68,1; 78,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,82; 82,81</t>
+          <t>72,52; 82,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76,91; 85,97</t>
+          <t>75,92; 85,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36,2; 46,02</t>
+          <t>37,46; 47,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>68,88; 76,59</t>
+          <t>68,85; 76,56</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>67,42; 75,36</t>
+          <t>67,7; 75,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76,71; 83,73</t>
+          <t>76,62; 83,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37,27; 44,94</t>
+          <t>38,73; 45,72</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>66,4%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>49,82; 58,06</t>
+          <t>49,48; 57,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>57,75; 65,48</t>
+          <t>57,94; 65,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81,61; 87,83</t>
+          <t>82,01; 87,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60,81; 69,64</t>
+          <t>62,6; 70,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,91; 53,84</t>
+          <t>45,84; 53,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,19; 75,18</t>
+          <t>68,1; 75,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,94; 90,81</t>
+          <t>86,02; 90,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>62,12; 69,71</t>
+          <t>63,16; 69,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>49,05; 54,81</t>
+          <t>48,89; 54,73</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64,15; 69,4</t>
+          <t>64,04; 69,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84,94; 88,66</t>
+          <t>84,67; 88,73</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,63; 68,77</t>
+          <t>63,45; 69,08</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>80,66; 85,92</t>
+          <t>80,12; 85,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>89,19; 93,23</t>
+          <t>89,11; 93,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91,02; 94,9</t>
+          <t>91,03; 94,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29,5; 86,47</t>
+          <t>82,71; 88,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>85,77; 90,51</t>
+          <t>86,03; 90,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>87,65; 91,97</t>
+          <t>87,44; 91,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>93,27; 96,37</t>
+          <t>93,12; 96,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>85,75; 90,18</t>
+          <t>85,98; 90,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>84,03; 87,54</t>
+          <t>83,9; 87,41</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>89,08; 92,06</t>
+          <t>89,21; 92,1</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>92,71; 95,25</t>
+          <t>92,74; 95,09</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>41,66; 87,55</t>
+          <t>85,13; 88,63</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>64,84%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>68,8; 72,01</t>
+          <t>68,69; 71,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>67,28; 70,62</t>
+          <t>67,23; 70,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>80,46; 83,29</t>
+          <t>80,47; 83,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>43,82; 63,62</t>
+          <t>62,57; 66,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>70,66; 73,79</t>
+          <t>70,83; 73,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>73,78; 76,72</t>
+          <t>73,9; 76,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>83,5; 86,03</t>
+          <t>83,39; 85,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>57,68; 64,72</t>
+          <t>63,9; 66,73</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>70,2; 72,44</t>
+          <t>70,27; 72,46</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71,07; 73,29</t>
+          <t>71,04; 73,28</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>82,49; 84,22</t>
+          <t>82,36; 84,23</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>51,86; 63,55</t>
+          <t>63,67; 66,08</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>163669</t>
+          <t>176498</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>172655</t>
+          <t>189723</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>336324</t>
+          <t>366221</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>209358; 233604</t>
+          <t>207728; 232976</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>207546; 238115</t>
+          <t>208809; 238332</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>227904; 253978</t>
+          <t>227315; 252625</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>141351; 185052</t>
+          <t>157071; 195620</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>227165; 246020</t>
+          <t>226731; 245211</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>226080; 249764</t>
+          <t>224846; 249545</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>227992; 251897</t>
+          <t>226995; 252291</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>158717; 185408</t>
+          <t>175326; 204142</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>442542; 472674</t>
+          <t>443562; 473793</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>442982; 479994</t>
+          <t>442270; 480020</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>466978; 499964</t>
+          <t>465749; 499443</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>310731; 362863</t>
+          <t>342201; 390288</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>325567</t>
+          <t>334220</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>295479</t>
+          <t>315202</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>621046</t>
+          <t>649421</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>284419; 330575</t>
+          <t>287331; 331943</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>260127; 307704</t>
+          <t>260553; 307479</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>394815; 430007</t>
+          <t>396966; 430315</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>293952; 353340</t>
+          <t>304348; 359031</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>328519; 367550</t>
+          <t>330512; 370387</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>282742; 329122</t>
+          <t>281848; 329789</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>409639; 444419</t>
+          <t>412484; 445611</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>274203; 315155</t>
+          <t>294416; 335833</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>624335; 683494</t>
+          <t>627567; 688972</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>554805; 622183</t>
+          <t>559021; 622236</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>819461; 865268</t>
+          <t>818783; 865087</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>585301; 656389</t>
+          <t>610876; 683850</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143821</t>
+          <t>146044</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>173868</t>
+          <t>181879</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>317689</t>
+          <t>327923</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>187046; 221856</t>
+          <t>186720; 221672</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>197610; 230130</t>
+          <t>196629; 231178</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>234440; 262906</t>
+          <t>234210; 262505</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126174; 161607</t>
+          <t>128970; 163124</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>176803; 213979</t>
+          <t>176856; 212714</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>241986; 271944</t>
+          <t>241806; 274142</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>262340; 287505</t>
+          <t>262184; 288527</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>157350; 187985</t>
+          <t>167194; 197848</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>375903; 424566</t>
+          <t>377562; 424538</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>446403; 496258</t>
+          <t>449764; 494316</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>504699; 542049</t>
+          <t>503472; 543632</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>296624; 341637</t>
+          <t>306104; 351815</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104296</t>
+          <t>126814</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>134707</t>
+          <t>153731</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>239003</t>
+          <t>280544</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>243776; 276242</t>
+          <t>243787; 276313</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>181304; 220903</t>
+          <t>180748; 219970</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>154453; 193491</t>
+          <t>156687; 197348</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84697; 127314</t>
+          <t>104921; 152398</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>247288; 281009</t>
+          <t>245759; 280899</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>224750; 264255</t>
+          <t>226924; 263711</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>205047; 243331</t>
+          <t>204559; 245053</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>83048; 170882</t>
+          <t>136043; 173658</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>501780; 547428</t>
+          <t>500094; 546323</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>416405; 472928</t>
+          <t>417307; 471687</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>369859; 428363</t>
+          <t>373035; 429183</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>172473; 280307</t>
+          <t>250927; 312456</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165395</t>
+          <t>188955</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>192391</t>
+          <t>210496</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>357786</t>
+          <t>399451</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>152696; 175809</t>
+          <t>153092; 175688</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>107888; 137534</t>
+          <t>108076; 136810</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>182090; 198748</t>
+          <t>181617; 198302</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>156333; 170676</t>
+          <t>179448; 195217</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>169044; 188305</t>
+          <t>168105; 188018</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>148750; 175455</t>
+          <t>147150; 173723</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>191187; 207149</t>
+          <t>190732; 207743</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>185531; 197280</t>
+          <t>202594; 216000</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>326947; 356598</t>
+          <t>328003; 358427</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>264511; 304195</t>
+          <t>263967; 303325</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>379695; 402712</t>
+          <t>379196; 401868</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>346099; 364972</t>
+          <t>388801; 409317</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>108964</t>
+          <t>115116</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>105239</t>
+          <t>111090</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>214203</t>
+          <t>226205</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>178994; 209533</t>
+          <t>178005; 208734</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>160608; 191286</t>
+          <t>157654; 190501</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>195628; 221494</t>
+          <t>195927; 221036</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>95320; 123231</t>
+          <t>101687; 131906</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>190600; 219080</t>
+          <t>189424; 218680</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>201646; 229294</t>
+          <t>200809; 227686</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>208558; 233139</t>
+          <t>205864; 232330</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>92908; 118117</t>
+          <t>98657; 123821</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>378112; 420428</t>
+          <t>377963; 420289</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>367927; 411246</t>
+          <t>369424; 412536</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>409885; 447377</t>
+          <t>409401; 446184</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>195768; 236088</t>
+          <t>206475; 243713</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>401914</t>
+          <t>469497</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>415313</t>
+          <t>501340</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>817228</t>
+          <t>970837</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>306393; 357057</t>
+          <t>304341; 354617</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>377647; 428193</t>
+          <t>378860; 429334</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>532025; 572591</t>
+          <t>534645; 572099</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>372863; 427035</t>
+          <t>442355; 501304</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>292548; 343080</t>
+          <t>292089; 344049</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>465030; 512682</t>
+          <t>464386; 513205</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>584402; 617481</t>
+          <t>584899; 618282</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>392033; 439966</t>
+          <t>477099; 525281</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>614174; 686318</t>
+          <t>612293; 685304</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>857001; 927140</t>
+          <t>855506; 927796</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1131314; 1180842</t>
+          <t>1127698; 1181878</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>779252; 855675</t>
+          <t>927629; 1010035</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>582845</t>
+          <t>681061</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>630412</t>
+          <t>728874</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1213257</t>
+          <t>1409935</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>598006; 637039</t>
+          <t>594046; 635373</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>689543; 720784</t>
+          <t>688898; 720185</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>705370; 735402</t>
+          <t>705450; 733911</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>272940; 800012</t>
+          <t>656816; 701410</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>671063; 708091</t>
+          <t>673076; 706623</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>719267; 754712</t>
+          <t>717560; 754796</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>767442; 792952</t>
+          <t>766162; 792772</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>613484; 645193</t>
+          <t>711942; 746268</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1280455; 1333922</t>
+          <t>1278449; 1331853</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1419641; 1467239</t>
+          <t>1421766; 1467830</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1481328; 1521897</t>
+          <t>1481677; 1519271</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>683443; 1436271</t>
+          <t>1381024; 1437692</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1996471</t>
+          <t>2238205</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2120065</t>
+          <t>2392335</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4116536</t>
+          <t>4630539</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2250039; 2355032</t>
+          <t>2246459; 2354550</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2278392; 2391339</t>
+          <t>2276496; 2387681</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2709949; 2805215</t>
+          <t>2710225; 2804228</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1494593; 2170174</t>
+          <t>2176876; 2301574</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2385562; 2491086</t>
+          <t>2391150; 2493440</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2599356; 2702639</t>
+          <t>2603273; 2701715</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2929722; 3018733</t>
+          <t>2925991; 3014856</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1955444; 2194019</t>
+          <t>2340477; 2443956</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4665905; 4815066</t>
+          <t>4670773; 4816316</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4910688; 5064090</t>
+          <t>4908312; 5063081</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5672689; 5791798</t>
+          <t>5663488; 5792360</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3527222; 4322024</t>
+          <t>4547219; 4719049</t>
         </is>
       </c>
     </row>
